--- a/lab_5/models/metrics/xgboost.xlsx
+++ b/lab_5/models/metrics/xgboost.xlsx
@@ -467,163 +467,163 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.9225</v>
+        <v>0.9142</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8174</v>
+        <v>0.8068</v>
       </c>
       <c r="C2" t="n">
-        <v>0.351</v>
+        <v>0.3143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.363</v>
+        <v>0.3028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3569</v>
+        <v>0.3084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3157</v>
+        <v>0.2627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3157</v>
+        <v>0.2627</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.9175</v>
+        <v>0.9124</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8257</v>
+        <v>0.8035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3133</v>
+        <v>0.3113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3197</v>
+        <v>0.2973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3165</v>
+        <v>0.3041</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2726</v>
+        <v>0.2574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2726</v>
+        <v>0.2575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.9216</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8223</v>
+        <v>0.8258</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3333</v>
+        <v>0.3429</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3497</v>
+        <v>0.3214</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3413</v>
+        <v>0.3318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2996</v>
+        <v>0.2869</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2997</v>
+        <v>0.2871</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9212</v>
+        <v>0.9176</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8207</v>
+        <v>0.7952</v>
       </c>
       <c r="C5" t="n">
-        <v>0.38</v>
+        <v>0.3143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3608</v>
+        <v>0.3204</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3701</v>
+        <v>0.3173</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3281</v>
+        <v>0.2735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3283</v>
+        <v>0.2735</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.9102</v>
+        <v>0.9153</v>
       </c>
       <c r="B6" t="n">
-        <v>0.802</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2781</v>
+        <v>0.381</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2727</v>
+        <v>0.3306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2754</v>
+        <v>0.354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2276</v>
+        <v>0.3089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2276</v>
+        <v>0.3098</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.9186</v>
+        <v>0.9151</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8176</v>
+        <v>0.8115</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3312</v>
+        <v>0.3327</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3332</v>
+        <v>0.3145</v>
       </c>
       <c r="E7" t="n">
-        <v>0.332</v>
+        <v>0.3231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2887</v>
+        <v>0.2779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2888</v>
+        <v>0.2781</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0045</v>
+        <v>0.0017</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0083</v>
+        <v>0.0124</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0344</v>
+        <v>0.0267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0339</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0335</v>
+        <v>0.0181</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0358</v>
+        <v>0.0185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0358</v>
+        <v>0.0188</v>
       </c>
     </row>
   </sheetData>
